--- a/lang/lv/headTags.xlsx
+++ b/lang/lv/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2027">
   <si>
     <t>en</t>
   </si>
@@ -4903,6 +4903,18 @@
     <t>Shulker</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (iedvesmots)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift (vaniļa)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -5692,6 +5704,9 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -5951,6 +5966,12 @@
   </si>
   <si>
     <t>Ziema</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>Ziemas kolekcija</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -6423,7 +6444,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1194"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14131,28 +14152,28 @@
         <v>1628</v>
       </c>
       <c r="B963" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B964" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B965" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B966" t="s">
         <v>1633</v>
@@ -14187,28 +14208,28 @@
         <v>1640</v>
       </c>
       <c r="B970" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B971" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="B972" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B973" t="s">
         <v>1645</v>
@@ -14251,36 +14272,36 @@
         <v>1654</v>
       </c>
       <c r="B978" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B979" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="B980" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="B981" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B982" t="s">
         <v>1660</v>
@@ -14371,28 +14392,28 @@
         <v>1681</v>
       </c>
       <c r="B993" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B994" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B995" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B996" t="s">
         <v>1686</v>
@@ -14419,36 +14440,36 @@
         <v>1691</v>
       </c>
       <c r="B999" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1000" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="B1001" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="B1002" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1003" t="s">
         <v>1697</v>
@@ -14483,20 +14504,20 @@
         <v>1704</v>
       </c>
       <c r="B1007" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1008" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1009" t="s">
         <v>1708</v>
@@ -14507,20 +14528,20 @@
         <v>1709</v>
       </c>
       <c r="B1010" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1011" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1012" t="s">
         <v>1713</v>
@@ -14563,36 +14584,36 @@
         <v>1722</v>
       </c>
       <c r="B1017" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1018" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="B1019" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="B1020" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B1021" t="s">
         <v>1728</v>
@@ -14603,28 +14624,28 @@
         <v>1729</v>
       </c>
       <c r="B1022" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B1023" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B1024" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1025" t="s">
         <v>1734</v>
@@ -14659,36 +14680,36 @@
         <v>1741</v>
       </c>
       <c r="B1029" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B1030" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="B1031" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="B1032" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B1033" t="s">
         <v>1747</v>
@@ -14699,28 +14720,28 @@
         <v>1748</v>
       </c>
       <c r="B1034" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B1035" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="B1036" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1037" t="s">
         <v>1753</v>
@@ -14747,84 +14768,84 @@
         <v>1758</v>
       </c>
       <c r="B1040" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B1041" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="B1042" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="B1043" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="B1044" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="B1045" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="B1046" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="B1047" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="B1048" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="B1049" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B1050" t="s">
         <v>1770</v>
@@ -14835,20 +14856,20 @@
         <v>1771</v>
       </c>
       <c r="B1051" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B1052" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B1053" t="s">
         <v>1775</v>
@@ -14867,20 +14888,20 @@
         <v>1778</v>
       </c>
       <c r="B1055" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B1056" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B1057" t="s">
         <v>1782</v>
@@ -14891,20 +14912,20 @@
         <v>1783</v>
       </c>
       <c r="B1058" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B1059" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B1060" t="s">
         <v>1787</v>
@@ -14923,20 +14944,20 @@
         <v>1790</v>
       </c>
       <c r="B1062" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B1063" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1064" t="s">
         <v>1794</v>
@@ -14995,20 +15016,20 @@
         <v>1807</v>
       </c>
       <c r="B1071" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1072" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1073" t="s">
         <v>1811</v>
@@ -15123,76 +15144,76 @@
         <v>1838</v>
       </c>
       <c r="B1087" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1088" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1089" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1090" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B1091" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B1092" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="B1093" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B1094" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B1095" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B1096" t="s">
         <v>1852</v>
@@ -15203,20 +15224,20 @@
         <v>1853</v>
       </c>
       <c r="B1097" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1098" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1099" t="s">
         <v>1857</v>
@@ -15283,20 +15304,20 @@
         <v>1872</v>
       </c>
       <c r="B1107" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1108" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B1109" t="s">
         <v>1876</v>
@@ -15331,20 +15352,20 @@
         <v>1883</v>
       </c>
       <c r="B1113" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="B1114" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="B1115" t="s">
         <v>1887</v>
@@ -15363,44 +15384,44 @@
         <v>1890</v>
       </c>
       <c r="B1117" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1118" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B1119" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B1120" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1121" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="B1122" t="s">
         <v>1898</v>
@@ -15411,20 +15432,20 @@
         <v>1899</v>
       </c>
       <c r="B1123" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1901</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B1125" t="s">
         <v>1903</v>
@@ -15443,12 +15464,12 @@
         <v>1906</v>
       </c>
       <c r="B1127" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1128" t="s">
         <v>1908</v>
@@ -15467,28 +15488,28 @@
         <v>1911</v>
       </c>
       <c r="B1130" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1913</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1914</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1915</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="B1133" t="s">
         <v>1917</v>
@@ -15515,20 +15536,20 @@
         <v>1922</v>
       </c>
       <c r="B1136" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1137" t="s">
         <v>1924</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>1925</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B1138" t="s">
         <v>1926</v>
@@ -15555,52 +15576,52 @@
         <v>1931</v>
       </c>
       <c r="B1141" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B1142" t="s">
         <v>1933</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>1934</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B1143" t="s">
         <v>1935</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>1936</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1144" t="s">
         <v>1937</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>1938</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1145" t="s">
         <v>1939</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1146" t="s">
         <v>1941</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>1942</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B1147" t="s">
         <v>1943</v>
@@ -15619,36 +15640,36 @@
         <v>1946</v>
       </c>
       <c r="B1149" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B1150" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B1151" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="B1152" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="B1153" t="s">
         <v>1952</v>
@@ -15667,28 +15688,28 @@
         <v>1954</v>
       </c>
       <c r="B1155" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="B1156" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="B1157" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="B1158" t="s">
         <v>1959</v>
@@ -15699,76 +15720,76 @@
         <v>1960</v>
       </c>
       <c r="B1159" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B1160" t="s">
         <v>1962</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>1963</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B1161" t="s">
         <v>1964</v>
-      </c>
-      <c r="B1161" t="s">
-        <v>1965</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B1162" t="s">
         <v>1966</v>
-      </c>
-      <c r="B1162" t="s">
-        <v>1967</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B1163" t="s">
         <v>1968</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>1969</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B1164" t="s">
         <v>1970</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>1971</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B1165" t="s">
         <v>1972</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>1973</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B1166" t="s">
         <v>1974</v>
-      </c>
-      <c r="B1166" t="s">
-        <v>1975</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1167" t="s">
         <v>1976</v>
-      </c>
-      <c r="B1167" t="s">
-        <v>1977</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B1168" t="s">
         <v>1978</v>
@@ -15803,20 +15824,20 @@
         <v>1985</v>
       </c>
       <c r="B1172" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B1173" t="s">
         <v>1987</v>
-      </c>
-      <c r="B1173" t="s">
-        <v>1988</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B1174" t="s">
         <v>1989</v>
@@ -15827,36 +15848,36 @@
         <v>1990</v>
       </c>
       <c r="B1175" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="B1176" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B1177" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="B1178" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B1179" t="s">
         <v>1997</v>
@@ -15867,76 +15888,76 @@
         <v>1998</v>
       </c>
       <c r="B1180" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B1181" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B1182" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="B1183" t="s">
-        <v>2001</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="B1184" t="s">
-        <v>2002</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="B1185" t="s">
-        <v>2003</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="B1186" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="B1187" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="B1188" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B1189" t="s">
         <v>2010</v>
@@ -15947,28 +15968,28 @@
         <v>2011</v>
       </c>
       <c r="B1190" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B1191" t="s">
         <v>2013</v>
-      </c>
-      <c r="B1191" t="s">
-        <v>2014</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1192" t="s">
         <v>2015</v>
-      </c>
-      <c r="B1192" t="s">
-        <v>2016</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B1193" t="s">
         <v>2017</v>
@@ -15982,8 +16003,40 @@
         <v>2019</v>
       </c>
     </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1194"/>
+  <autoFilter ref="A1:B1198"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
